--- a/data_out/country_spreadsheets/Netherlands.xlsx
+++ b/data_out/country_spreadsheets/Netherlands.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W41"/>
+  <dimension ref="A1:AN41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,87 +461,172 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Median drought days per year</t>
+          <t>Median drought-warning-days</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Maximum recorded drought days per year</t>
+          <t>Maximum recorded drought-warning-days</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>most severe drought year</t>
+          <t>Year of maximum drought-warning-days</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2012</t>
+          <t>Warning days 2012</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2013</t>
+          <t>Warning days 2013</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2014</t>
+          <t>Warning days 2014</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2015</t>
+          <t>Warning days 2015</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2016</t>
+          <t>Warning days 2016</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2017</t>
+          <t>Warning days 2017</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2018</t>
+          <t>Warning days 2018</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2019</t>
+          <t>Warning days 2019</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2020</t>
+          <t>Warning days 2020</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2021</t>
+          <t>Warning days 2021</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2022</t>
+          <t>Warning days 2022</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2023</t>
+          <t>Warning days 2023</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2024</t>
+          <t>Warning days 2024</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2025</t>
+          <t>Warning days 2025</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Median drought-alert-days</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Maximum recorded drought-alert-days</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Year of maximum drought-alert-days</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2012</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2013</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2014</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2015</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2016</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2017</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2018</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2019</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2020</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2021</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2022</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2023</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2024</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2025</t>
         </is>
       </c>
     </row>
@@ -621,6 +706,57 @@
       <c r="W2" t="n">
         <v>106.07</v>
       </c>
+      <c r="X2" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>46.76</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>32.92</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>60.62</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>28.16</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>38.83</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>52.35</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>190.21</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>170.1</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>123.38</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>131.54</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>106.07</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -698,6 +834,57 @@
       <c r="W3" t="n">
         <v>110.98</v>
       </c>
+      <c r="X3" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>53.14</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>27.62</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>66.38</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>100.27</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>51.76</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>184.21</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>141.83</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>112.24</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>116.42</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>38.92</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>110.98</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -775,6 +962,57 @@
       <c r="W4" t="n">
         <v>136.5</v>
       </c>
+      <c r="X4" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>47.33</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>28.31</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>71.41</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>123.01</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>20.45</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>61.61</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>66.48999999999999</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>177.83</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>134.81</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>126.76</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>61.95</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>136.5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -852,6 +1090,57 @@
       <c r="W5" t="n">
         <v>162.21</v>
       </c>
+      <c r="X5" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>45.11</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>23.95</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>109.94</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>40.26</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>104.93</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>185.44</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>114.4</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>87.02</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>162.21</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -929,6 +1218,57 @@
       <c r="W6" t="n">
         <v>148.84</v>
       </c>
+      <c r="X6" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>33.22</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>11.94</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>118.39</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>31.06</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>23.86</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>98.91</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>169.84</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>217.06</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>193.89</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>163.3</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>157.15</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>62.48</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>148.84</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1006,6 +1346,57 @@
       <c r="W7" t="n">
         <v>161.73</v>
       </c>
+      <c r="X7" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>54.04</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>30.63</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>71.81999999999999</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>43.99</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>92.13</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>227.21</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>134.45</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>144.62</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>127.61</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>78.26000000000001</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>161.73</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1083,6 +1474,57 @@
       <c r="W8" t="n">
         <v>95.29000000000001</v>
       </c>
+      <c r="X8" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>56.13</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>31.17</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>64.55</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>54.48</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>198.07</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>147.29</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>140.15</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>107.59</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>62.95</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>95.29000000000001</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1160,6 +1602,57 @@
       <c r="W9" t="n">
         <v>133.38</v>
       </c>
+      <c r="X9" t="n">
+        <v>8.91</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>48.39</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>41.61</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>67.77</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>22.08</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>59.58</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>196.09</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>169.73</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>115.13</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>51.31</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>133.38</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1237,6 +1730,57 @@
       <c r="W10" t="n">
         <v>114.08</v>
       </c>
+      <c r="X10" t="n">
+        <v>16.66</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>50.55</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>37.16</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>57.43</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>79.55</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>198.2</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>141.37</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>144.5</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>142.82</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>50.44</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>114.08</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1314,6 +1858,57 @@
       <c r="W11" t="n">
         <v>85.41</v>
       </c>
+      <c r="X11" t="n">
+        <v>10.16</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>45.18</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>30.04</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>62.87</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>13.77</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>31.26</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>105.82</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>211.61</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>147.29</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>174.97</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>167.55</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>62.62</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>85.41</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1391,6 +1986,57 @@
       <c r="W12" t="n">
         <v>65.59999999999999</v>
       </c>
+      <c r="X12" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>45.34</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>30.77</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>43.49</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>11.26</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>109.51</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>208.19</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>144.66</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>202.33</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>180.83</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>50.88</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>65.59999999999999</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1468,6 +2114,57 @@
       <c r="W13" t="n">
         <v>72.90000000000001</v>
       </c>
+      <c r="X13" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>47.88</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>13.38</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>93.05</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>207.26</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>187.08</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>180.04</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>191.62</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>55.12</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>72.90000000000001</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1545,6 +2242,57 @@
       <c r="W14" t="n">
         <v>153.97</v>
       </c>
+      <c r="X14" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>11.03</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>14.93</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>13.76</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>90.91</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>201.55</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>156.51</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>176.46</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>152.1</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>43.54</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>153.97</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1622,6 +2370,57 @@
       <c r="W15" t="n">
         <v>237.06</v>
       </c>
+      <c r="X15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>55.95</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>47.71</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>46.33</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>74.86</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>185.23</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>182.17</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>200.56</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>183.96</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>13.58</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>108.79</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>43.91</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>237.06</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1699,6 +2498,57 @@
       <c r="W16" t="n">
         <v>96.95</v>
       </c>
+      <c r="X16" t="n">
+        <v>8.67</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>48.83</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>34.65</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>41.58</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>24.44</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>85.62</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>204.35</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>176.59</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>188.02</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>189.88</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>30.67</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>96.95</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1776,6 +2626,57 @@
       <c r="W17" t="n">
         <v>216.65</v>
       </c>
+      <c r="X17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>38.15</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>65.06999999999999</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>28.82</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>15.62</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>97.25</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>188.37</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>205.65</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>215.63</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>167.42</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>37.65</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>216.65</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1853,6 +2754,57 @@
       <c r="W18" t="n">
         <v>82.84999999999999</v>
       </c>
+      <c r="X18" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>32.12</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>27.95</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>101.91</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>21.35</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>29.17</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>45.07</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>121.8</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>228.63</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>202.6</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>154.16</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>174.51</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>66.51000000000001</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>82.84999999999999</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -1930,6 +2882,57 @@
       <c r="W19" t="n">
         <v>223.51</v>
       </c>
+      <c r="X19" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>26.95</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>21.24</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>51.48</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>16.08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>41.64</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>105.28</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>202.63</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>111.62</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>189.97</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>12.17</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>94.98</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>45.92</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>223.51</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -2007,6 +3010,57 @@
       <c r="W20" t="n">
         <v>115.04</v>
       </c>
+      <c r="X20" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>38.84</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>39.43</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>123.06</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>14.62</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>27.93</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>33.51</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>136.68</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>187.07</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>119.34</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>99.58</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>116.95</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>115.04</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -2084,6 +3138,57 @@
       <c r="W21" t="n">
         <v>192.46</v>
       </c>
+      <c r="X21" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>87.44</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>62.28</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>25.93</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>100.11</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>144.57</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>129.91</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>125.91</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>12.27</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>110.91</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>62.74</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>192.46</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -2161,6 +3266,57 @@
       <c r="W22" t="n">
         <v>171.52</v>
       </c>
+      <c r="X22" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>38.62</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>66.81999999999999</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>63.49</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>16.32</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>70.42</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>142.69</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>111.72</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>113.21</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>17.22</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>84.83</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>53.43</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>171.52</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -2238,6 +3394,57 @@
       <c r="W23" t="n">
         <v>196.78</v>
       </c>
+      <c r="X23" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>37.69</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>25.45</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>68.02</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>52.68</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>126.11</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>197.45</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>142.14</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>149.87</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>134.68</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>59.46</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>196.78</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -2315,6 +3522,57 @@
       <c r="W24" t="n">
         <v>168.8</v>
       </c>
+      <c r="X24" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>19.65</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>41.02</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>71.73</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>18.36</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>56.58</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>92.34</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>222.57</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>137.09</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>186.41</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>56.47</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>168.8</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -2392,6 +3650,57 @@
       <c r="W25" t="n">
         <v>182.17</v>
       </c>
+      <c r="X25" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>48.32</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>39.83</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>106.29</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>16.02</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>14.41</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>120.77</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>180.72</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>105.94</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>110.47</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>113.01</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>52.99</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>182.17</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -2469,6 +3778,57 @@
       <c r="W26" t="n">
         <v>154.19</v>
       </c>
+      <c r="X26" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>19.13</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>41.23</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>75.15000000000001</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>59.13</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>81.41</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>209.44</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>128.92</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>156.84</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>108.78</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>46.06</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>154.19</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -2546,6 +3906,57 @@
       <c r="W27" t="n">
         <v>202.31</v>
       </c>
+      <c r="X27" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>24.52</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>15.36</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>57.64</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>44.18</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>87.23</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>143.37</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>61.61</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>55.85</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>95.58</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>202.31</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -2623,6 +4034,57 @@
       <c r="W28" t="n">
         <v>246.75</v>
       </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2017</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>13.09</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>39.72</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>12.26</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>49.64</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>48.72</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>95.15000000000001</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>155.73</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>103.22</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>99.17</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>12.21</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>83.73999999999999</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>246.75</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -2700,6 +4162,57 @@
       <c r="W29" t="n">
         <v>196.29</v>
       </c>
+      <c r="X29" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>45.92</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>38.02</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>79.31</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>7.59</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>58.79</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>82.51000000000001</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>169.87</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>88.84999999999999</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>82.23</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>42.93</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>196.29</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -2777,6 +4290,57 @@
       <c r="W30" t="n">
         <v>273.47</v>
       </c>
+      <c r="X30" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>21.86</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2018</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>10.21</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>17.19</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>23.12</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>74.53</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>213.1</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>180.34</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>226.48</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>152.11</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>16.37</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>134.24</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>38.24</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>273.47</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -2854,6 +4418,57 @@
       <c r="W31" t="n">
         <v>251.84</v>
       </c>
+      <c r="X31" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>19.42</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>33.42</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>46.41</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>50.29</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>67.33</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>176.13</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>185.05</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>176.63</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>129.5</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>125.28</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>42.71</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>251.84</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -2931,6 +4546,57 @@
       <c r="W32" t="n">
         <v>235.1</v>
       </c>
+      <c r="X32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>14.49</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>35.62</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>61.43</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>63.02</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>147.31</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>153.93</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>122.6</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>94.29000000000001</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>157.22</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>71.25</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>235.1</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -3008,6 +4674,57 @@
       <c r="W33" t="n">
         <v>161.47</v>
       </c>
+      <c r="X33" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>28.55</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>24.37</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>65.11</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>53.89</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>133.58</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>136.19</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>172.02</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>158.52</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>23.49</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>128.65</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>50.55</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>161.47</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -3085,6 +4802,57 @@
       <c r="W34" t="n">
         <v>162.35</v>
       </c>
+      <c r="X34" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>33.28</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>15.13</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>42.81</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>36.54</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>74.31999999999999</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>40.27</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>99.65000000000001</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>130.87</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>126.45</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>39.55</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>115.86</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>162.35</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -3162,6 +4930,57 @@
       <c r="W35" t="n">
         <v>248.89</v>
       </c>
+      <c r="X35" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>53.36</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>17.67</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>50.76</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>25.24</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>60.78</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>31.32</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>110.99</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>182.13</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>188.5</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>162.87</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>24.53</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>130.02</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>52.01</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>248.89</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -3239,6 +5058,57 @@
       <c r="W36" t="n">
         <v>252.04</v>
       </c>
+      <c r="X36" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>52.79</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>15.96</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>33.99</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>28.92</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>32.16</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>138.56</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>187.21</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>185.74</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>158.13</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>110.34</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>44.76</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>252.04</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -3316,6 +5186,57 @@
       <c r="W37" t="n">
         <v>204.23</v>
       </c>
+      <c r="X37" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>49.13</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>39.12</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>27.04</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>96.31</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>185.55</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>260.27</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>215.43</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>25.17</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>111.44</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>51.59</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>204.23</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -3393,6 +5314,57 @@
       <c r="W38" t="n">
         <v>219.81</v>
       </c>
+      <c r="X38" t="n">
+        <v>9.59</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>19.12</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>23.27</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>40.64</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>96.89</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>185.57</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>243.73</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>223.34</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>46.25</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>153.74</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>66.18000000000001</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>219.81</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -3470,6 +5442,57 @@
       <c r="W39" t="n">
         <v>73.04000000000001</v>
       </c>
+      <c r="X39" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>36.69</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2020</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>29.31</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>45.24</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>41.85</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>35.71</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>186.55</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>189.69</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>227.44</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>37.36</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>89.98</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>35.96</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>73.04000000000001</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
@@ -3547,6 +5570,57 @@
       <c r="W40" t="n">
         <v>93.92</v>
       </c>
+      <c r="X40" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>28.36</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2018</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>27.66</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>15.01</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>58.63</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>50.31</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>92.87</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>192.8</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>162.58</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>266.73</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>36.36</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>102.72</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>31.71</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>93.92</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
@@ -3622,6 +5696,57 @@
         <v>0</v>
       </c>
       <c r="W41" t="n">
+        <v>214.27</v>
+      </c>
+      <c r="X41" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>19.46</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>25.29</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>35.66</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>158.39</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>30.57</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>157.09</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>186.97</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>129.78</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>219.05</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>31.16</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>229.56</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>92.83</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN41" t="n">
         <v>214.27</v>
       </c>
     </row>
